--- a/asset-forge/products/P13_DEMO_Compliance_Gap_Analysis_Mock_Audit.xlsx
+++ b/asset-forge/products/P13_DEMO_Compliance_Gap_Analysis_Mock_Audit.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00 · Start Here · Začnite tu" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01 · Gap Analysis · Analýza" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02 · Mock Audit · Skúšobný audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03 · Readiness · Pripravenosť" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04 · Next Steps · Ďalšie kroky" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DEMO Preview · Ukážka" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="00 · Start Here · Začnite tu" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="01 · Gap Analysis · Analýza" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="02 · Mock Audit · Skúška" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="03 · Readiness · Pripravenosť" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="04 · Next Steps · Ďalšie kroky" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -183,6 +184,29 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F3A5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -307,9 +331,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -850,11 +883,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMO — PREVIEW ONLY · NOT FOR RESALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ukážka — len na náhľad · nie na ďalší predaj</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>This is a locked, read-only preview of the workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Toto je uzamknutý náhľad zošita len na čítanie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Browse the tabs to see the Gap Analysis, Mock Audit, Readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>verdict and Next Steps. Buy the full pack to unlock editing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Prehliadnite si hárky. Kúpou plnej verzie odomknete úpravy.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CA8B"/>
+  <mergeCells count="9">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001F3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -867,220 +989,211 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMO — PREVIEW ONLY · enter your email to download the free editable file · ukážka — zadajte e-mail a stiahnite si bezplatný upraviteľný súbor</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>COMPLIANCE GAP-ANALYSIS &amp; MOCK-AUDIT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>COMPLIANCE GAP-ANALYSIS &amp; MOCK-AUDIT</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Analýza nedostatkov a skúšobný audit — „Prejdem auditom?“</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Analýza nedostatkov a skúšobný audit — „Prejdem auditom?“</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Score your readiness in 15 minutes · Ohodnoťte svoju pripravenosť za 15 minút</t>
         </is>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>WHAT'S INSIDE / ČO OBSAHUJE</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>WHAT'S INSIDE / ČO OBSAHUJE</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>01 · Clause-by-clause Gap Analysis</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Analýza nedostatkov po jednotlivých bodoch</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>01 · Clause-by-clause Gap Analysis</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Analýza nedostatkov po jednotlivých bodoch</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>02 · Mock-Audit Readiness Self-Assessment</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Skúšobný audit — sebahodnotenie pripravenosti</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>02 · Mock-Audit Readiness Self-Assessment</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Skúšobný audit — sebahodnotenie pripravenosti</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>03 · Readiness Score &amp; Verdict (RAG)</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Skóre pripravenosti a verdikt (RAG)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>03 · Readiness Score &amp; Verdict (RAG)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Skóre pripravenosti a verdikt (RAG)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="6" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>04 · Next Steps — which kit closes your gaps</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Ďalšie kroky — ktorý balík vyrieši vaše medzery</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1"/>
+    <row r="11" ht="6" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>WHAT IT IS / ČO TO JE</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>WHAT IT IS / ČO TO JE</t>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>A generic readiness check across the common management-system spine</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Všeobecná kontrola pripravenosti naprieč spoločnou kostrou systému riadenia</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>A generic readiness check across the common management-system spine</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Všeobecná kontrola pripravenosti naprieč spoločnou kostrou systému riadenia</t>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>(ISO 9001 · ISO 22000 · HACCP · BRCGS · IFS · FSSC 22000 structure)</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>(štruktúra ISO 9001 · ISO 22000 · HACCP · BRCGS · IFS · FSSC 22000)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>(ISO 9001 · ISO 22000 · HACCP · BRCGS · IFS · FSSC 22000 structure)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>(štruktúra ISO 9001 · ISO 22000 · HACCP · BRCGS · IFS · FSSC 22000)</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Audit-ready for a TÜV-style certifier auditing you to these standards —</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Pripravené pre certifikačný orgán (štýl TÜV), ktorý vás audituje podľa týchto noriem —</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Audit-ready for a TÜV-style certifier auditing you to these standards —</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Pripravené pre certifikačný orgán (štýl TÜV), ktorý vás audituje podľa týchto noriem —</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="6" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>NOT a 'TÜV template'. TÜV is a certifier, not a standard.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>NIE je to „TÜV šablóna“. TÜV je certifikačný orgán, nie norma.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1"/>
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>HOW TO USE / AKO POUŽÍVAŤ</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>HOW TO USE / AKO POUŽÍVAŤ</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>1. On Sheet 01, set a Status for each clause (dropdown).</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>1. Na hárku 01 nastavte stav pre každý bod (rozbaľovací zoznam).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>1. On Sheet 01, set a Status for each clause (dropdown).</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>1. Na hárku 01 nastavte stav pre každý bod (rozbaľovací zoznam).</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2. On Sheet 02, answer the 20 mock-audit questions.</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>2. Na hárku 02 odpovedzte na 20 otázok skúšobného auditu.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>2. On Sheet 02, answer the 20 mock-audit questions.</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>2. Na hárku 02 odpovedzte na 20 otázok skúšobného auditu.</t>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>3. Sheet 03 auto-calculates your readiness % and verdict.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>3. Hárok 03 automaticky vypočíta % pripravenosti a verdikt.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>3. Sheet 03 auto-calculates your readiness % and verdict.</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>3. Hárok 03 automaticky vypočíta % pripravenosti a verdikt.</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>4. Sheet 04 routes you to the kit that closes the gaps.</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>4. Hárok 04 vás nasmeruje na balík, ktorý medzery vyrieši.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>4. Sheet 04 routes you to the kit that closes the gaps.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>4. Hárok 04 vás nasmeruje na balík, ktorý medzery vyrieši.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Amber = you fill · Green/Red = auto-scored · Grey = guidance.</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Oranžová = vyplníte · Zelená/červená = automaticky · Sivá = pokyny.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1"/>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>ASSET-FORGE · v1.0 · 30/05/2026 · EU (Ireland) · FREE lead magnet · Template only — not legal advice nor a guarantee of certification. · Šablóna — nie je právne poradenstvo ani záruka certifikácie.</t>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ASSET-FORGE · v1.1 · 30/05/2026 · EU (Ireland) · FREE lead magnet · Template only — not legal advice nor a guarantee of certification. · Šablóna — nie je právne poradenstvo ani záruka certifikácie.</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1238,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002A7D7B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1145,875 +1258,867 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMO — PREVIEW ONLY · enter your email to download the free editable file · ukážka — zadajte e-mail a stiahnite si bezplatný upraviteľný súbor</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Clause-by-clause Gap Analysis  |  Analýza nedostatkov po jednotlivých bodoch</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Clause-by-clause Gap Analysis  |  Analýza nedostatkov po jednotlivých bodoch</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Current state vs each requirement — % conformance auto-rolls up to Sheet 03  ·  Aktuálny stav vs každá požiadavka — % zhody sa prenáša na hárok 03</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Current state vs each requirement — % conformance auto-rolls up to Sheet 03  ·  Aktuálny stav vs každá požiadavka — % zhody sa prenáša na hárok 03</t>
-        </is>
-      </c>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Business name / Názov prevádzky:</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Business name / Názov prevádzky:</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr"/>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Standard / scheme assessed / Posudzovaná norma / schéma:</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Standard / scheme assessed / Posudzovaná norma / schéma:</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr"/>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Date assessed (DD/MM/YYYY) / Dátum posúdenia:</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Date assessed (DD/MM/YYYY) / Dátum posúdenia:</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>ℹ  Set a Status per clause: Conform (100%) · Partial (50%) · Not in place (0%) · N/A (excluded). Conformance % and Priority fill automatically. Non-food businesses set the 8F food rows to N/A.
     Nastavte stav: Zhoda (100 %) · Čiastočne (50 %) · Chýba (0 %) · Neaplikuje (vylúčené). % zhody a priorita sa vyplnia automaticky. Nepotravinárske prevádzky nastavia riadky 8F na Neaplikuje.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Section
 Sekcia</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Clause
 Bod</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Requirement
 Požiadavka</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Status
 Stav</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Conf. %
 Zhoda %</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Evidence / where
 Dôkaz / kde</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Action to close
 Opatrenie</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Priority
 Priorita</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>4 · Context / Kontext</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Internal &amp; external issues affecting the business are identified
 Interné a externé faktory ovplyvňujúce prevádzku sú identifikované</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr"/>
-      <c r="E10" s="19">
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="22">
         <f>IF(D9="","",IF(LEFT(D9,3)="Con",1,IF(LEFT(D9,3)="Par",0.5,IF(LEFT(D9,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="20">
+      <c r="F9" s="15" t="inlineStr"/>
+      <c r="G9" s="15" t="inlineStr"/>
+      <c r="H9" s="23">
         <f>IF(D9="","",IF(LEFT(D9,3)="Not","HIGH",IF(LEFT(D9,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>4 · Context / Kontext</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Needs &amp; expectations of interested parties (customers, regulators) recorded
 Potreby a očakávania zainteresovaných strán sú zaznamenané</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="19">
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="22">
         <f>IF(D10="","",IF(LEFT(D10,3)="Con",1,IF(LEFT(D10,3)="Par",0.5,IF(LEFT(D10,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F11" s="12" t="inlineStr"/>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="20">
+      <c r="F10" s="15" t="inlineStr"/>
+      <c r="G10" s="15" t="inlineStr"/>
+      <c r="H10" s="23">
         <f>IF(D10="","",IF(LEFT(D10,3)="Not","HIGH",IF(LEFT(D10,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>4 · Context / Kontext</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>4.3/4.4</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Scope of the management system is defined and key processes are mapped
 Rozsah systému riadenia je definovaný a kľúčové procesy zmapované</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr"/>
-      <c r="E12" s="19">
+      <c r="D11" s="21" t="inlineStr"/>
+      <c r="E11" s="22">
         <f>IF(D11="","",IF(LEFT(D11,3)="Con",1,IF(LEFT(D11,3)="Par",0.5,IF(LEFT(D11,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr"/>
-      <c r="H12" s="20">
+      <c r="F11" s="15" t="inlineStr"/>
+      <c r="G11" s="15" t="inlineStr"/>
+      <c r="H11" s="23">
         <f>IF(D11="","",IF(LEFT(D11,3)="Not","HIGH",IF(LEFT(D11,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>5 · Leadership / Vedenie</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Top management demonstrably commits to and resources the system
 Vrcholový manažment preukázateľne podporuje a zdrojuje systém</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr"/>
-      <c r="E13" s="19">
+      <c r="D12" s="21" t="inlineStr"/>
+      <c r="E12" s="22">
         <f>IF(D12="","",IF(LEFT(D12,3)="Con",1,IF(LEFT(D12,3)="Par",0.5,IF(LEFT(D12,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="20">
+      <c r="F12" s="15" t="inlineStr"/>
+      <c r="G12" s="15" t="inlineStr"/>
+      <c r="H12" s="23">
         <f>IF(D12="","",IF(LEFT(D12,3)="Not","HIGH",IF(LEFT(D12,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>5 · Leadership / Vedenie</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>A policy is documented, communicated and available to staff
 Politika je zdokumentovaná, komunikovaná a dostupná zamestnancom</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr"/>
-      <c r="E14" s="19">
+      <c r="D13" s="21" t="inlineStr"/>
+      <c r="E13" s="22">
         <f>IF(D13="","",IF(LEFT(D13,3)="Con",1,IF(LEFT(D13,3)="Par",0.5,IF(LEFT(D13,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr"/>
-      <c r="H14" s="20">
+      <c r="F13" s="15" t="inlineStr"/>
+      <c r="G13" s="15" t="inlineStr"/>
+      <c r="H13" s="23">
         <f>IF(D13="","",IF(LEFT(D13,3)="Not","HIGH",IF(LEFT(D13,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>5 · Leadership / Vedenie</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Roles, responsibilities and authorities are assigned and understood
 Úlohy, zodpovednosti a právomoci sú pridelené a pochopené</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr"/>
-      <c r="E15" s="19">
+      <c r="D14" s="21" t="inlineStr"/>
+      <c r="E14" s="22">
         <f>IF(D14="","",IF(LEFT(D14,3)="Con",1,IF(LEFT(D14,3)="Par",0.5,IF(LEFT(D14,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="20">
+      <c r="F14" s="15" t="inlineStr"/>
+      <c r="G14" s="15" t="inlineStr"/>
+      <c r="H14" s="23">
         <f>IF(D14="","",IF(LEFT(D14,3)="Not","HIGH",IF(LEFT(D14,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>6 · Planning / Plánovanie</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Risks &amp; opportunities are assessed (incl. climate, Amd 1:2024)
 Riziká a príležitosti sú posúdené (vrátane klímy, dodatok 1:2024)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr"/>
-      <c r="E16" s="19">
+      <c r="D15" s="21" t="inlineStr"/>
+      <c r="E15" s="22">
         <f>IF(D15="","",IF(LEFT(D15,3)="Con",1,IF(LEFT(D15,3)="Par",0.5,IF(LEFT(D15,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="20">
+      <c r="F15" s="15" t="inlineStr"/>
+      <c r="G15" s="15" t="inlineStr"/>
+      <c r="H15" s="23">
         <f>IF(D15="","",IF(LEFT(D15,3)="Not","HIGH",IF(LEFT(D15,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>6 · Planning / Plánovanie</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Objectives are set, measurable, with plans to achieve them
 Ciele sú stanovené, merateľné a s plánom na ich dosiahnutie</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr"/>
-      <c r="E17" s="19">
+      <c r="D16" s="21" t="inlineStr"/>
+      <c r="E16" s="22">
         <f>IF(D16="","",IF(LEFT(D16,3)="Con",1,IF(LEFT(D16,3)="Par",0.5,IF(LEFT(D16,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="12" t="inlineStr"/>
-      <c r="H17" s="20">
+      <c r="F16" s="15" t="inlineStr"/>
+      <c r="G16" s="15" t="inlineStr"/>
+      <c r="H16" s="23">
         <f>IF(D16="","",IF(LEFT(D16,3)="Not","HIGH",IF(LEFT(D16,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>6 · Planning / Plánovanie</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Changes to the system are planned and controlled
 Zmeny systému sú plánované a riadené</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr"/>
-      <c r="E18" s="19">
+      <c r="D17" s="21" t="inlineStr"/>
+      <c r="E17" s="22">
         <f>IF(D17="","",IF(LEFT(D17,3)="Con",1,IF(LEFT(D17,3)="Par",0.5,IF(LEFT(D17,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="20">
+      <c r="F17" s="15" t="inlineStr"/>
+      <c r="G17" s="15" t="inlineStr"/>
+      <c r="H17" s="23">
         <f>IF(D17="","",IF(LEFT(D17,3)="Not","HIGH",IF(LEFT(D17,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>7 · Support / Podpora</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Resources, infrastructure and work environment are provided
 Zdroje, infraštruktúra a pracovné prostredie sú zabezpečené</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr"/>
-      <c r="E19" s="19">
+      <c r="D18" s="21" t="inlineStr"/>
+      <c r="E18" s="22">
         <f>IF(D18="","",IF(LEFT(D18,3)="Con",1,IF(LEFT(D18,3)="Par",0.5,IF(LEFT(D18,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr"/>
-      <c r="H19" s="20">
+      <c r="F18" s="15" t="inlineStr"/>
+      <c r="G18" s="15" t="inlineStr"/>
+      <c r="H18" s="23">
         <f>IF(D18="","",IF(LEFT(D18,3)="Not","HIGH",IF(LEFT(D18,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>7 · Support / Podpora</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Competence: training needs identified and training records kept
 Kompetencie: potreby školenia určené a záznamy o školení vedené</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr"/>
-      <c r="E20" s="19">
+      <c r="D19" s="21" t="inlineStr"/>
+      <c r="E19" s="22">
         <f>IF(D19="","",IF(LEFT(D19,3)="Con",1,IF(LEFT(D19,3)="Par",0.5,IF(LEFT(D19,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr"/>
-      <c r="H20" s="20">
+      <c r="F19" s="15" t="inlineStr"/>
+      <c r="G19" s="15" t="inlineStr"/>
+      <c r="H19" s="23">
         <f>IF(D19="","",IF(LEFT(D19,3)="Not","HIGH",IF(LEFT(D19,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>7 · Support / Podpora</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>7.3/7.4</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Staff are aware of the policy; communication is defined
 Zamestnanci poznajú politiku; komunikácia je definovaná</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr"/>
-      <c r="E21" s="19">
+      <c r="D20" s="21" t="inlineStr"/>
+      <c r="E20" s="22">
         <f>IF(D20="","",IF(LEFT(D20,3)="Con",1,IF(LEFT(D20,3)="Par",0.5,IF(LEFT(D20,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="20">
+      <c r="F20" s="15" t="inlineStr"/>
+      <c r="G20" s="15" t="inlineStr"/>
+      <c r="H20" s="23">
         <f>IF(D20="","",IF(LEFT(D20,3)="Not","HIGH",IF(LEFT(D20,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>7 · Support / Podpora</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Documented information is version-controlled, approved and retrievable
 Dokumentácia má riadené verzie, je schválená a dohľadateľná</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr"/>
-      <c r="E22" s="19">
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="22">
         <f>IF(D21="","",IF(LEFT(D21,3)="Con",1,IF(LEFT(D21,3)="Par",0.5,IF(LEFT(D21,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F22" s="12" t="inlineStr"/>
-      <c r="G22" s="12" t="inlineStr"/>
-      <c r="H22" s="20">
+      <c r="F21" s="15" t="inlineStr"/>
+      <c r="G21" s="15" t="inlineStr"/>
+      <c r="H21" s="23">
         <f>IF(D21="","",IF(LEFT(D21,3)="Not","HIGH",IF(LEFT(D21,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>8 · Operation / Prevádzka</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>Operational processes are planned and controlled
 Prevádzkové procesy sú plánované a riadené</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr"/>
-      <c r="E23" s="19">
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="22">
         <f>IF(D22="","",IF(LEFT(D22,3)="Con",1,IF(LEFT(D22,3)="Par",0.5,IF(LEFT(D22,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="20">
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="15" t="inlineStr"/>
+      <c r="H22" s="23">
         <f>IF(D22="","",IF(LEFT(D22,3)="Not","HIGH",IF(LEFT(D22,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>8 · Operation / Prevádzka</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Work instructions / SOPs exist and are followed in practice
 Pracovné postupy (SOP) existujú a v praxi sa dodržiavajú</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr"/>
-      <c r="E24" s="19">
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="22">
         <f>IF(D23="","",IF(LEFT(D23,3)="Con",1,IF(LEFT(D23,3)="Par",0.5,IF(LEFT(D23,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F24" s="12" t="inlineStr"/>
-      <c r="G24" s="12" t="inlineStr"/>
-      <c r="H24" s="20">
+      <c r="F23" s="15" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr"/>
+      <c r="H23" s="23">
         <f>IF(D23="","",IF(LEFT(D23,3)="Not","HIGH",IF(LEFT(D23,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>8 · Operation / Prevádzka</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>Externally provided products/services controlled (suppliers approved)
 Externé produkty/služby sú riadené (dodávatelia schválení)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr"/>
-      <c r="E25" s="19">
+      <c r="D24" s="21" t="inlineStr"/>
+      <c r="E24" s="22">
         <f>IF(D24="","",IF(LEFT(D24,3)="Con",1,IF(LEFT(D24,3)="Par",0.5,IF(LEFT(D24,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F25" s="12" t="inlineStr"/>
-      <c r="G25" s="12" t="inlineStr"/>
-      <c r="H25" s="20">
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
+      <c r="H24" s="23">
         <f>IF(D24="","",IF(LEFT(D24,3)="Not","HIGH",IF(LEFT(D24,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>8F · Food Safety / Bezpečnosť potravín</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>HACCP</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>HACCP / PRP plan documented with CCPs and critical limits
 HACCP / PRP plán s kritickými bodmi (CCP) a kritickými limitmi</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr"/>
-      <c r="E26" s="19">
+      <c r="D25" s="21" t="inlineStr"/>
+      <c r="E25" s="22">
         <f>IF(D25="","",IF(LEFT(D25,3)="Con",1,IF(LEFT(D25,3)="Par",0.5,IF(LEFT(D25,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="12" t="inlineStr"/>
-      <c r="H26" s="20">
+      <c r="F25" s="15" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr"/>
+      <c r="H25" s="23">
         <f>IF(D25="","",IF(LEFT(D25,3)="Not","HIGH",IF(LEFT(D25,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>8F · Food Safety / Bezpečnosť potravín</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>FIC</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>Allergen management &amp; labelling in place (Reg. 1169/2011)
 Riadenie alergénov a označovanie zavedené (nar. 1169/2011)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr"/>
-      <c r="E27" s="19">
+      <c r="D26" s="21" t="inlineStr"/>
+      <c r="E26" s="22">
         <f>IF(D26="","",IF(LEFT(D26,3)="Con",1,IF(LEFT(D26,3)="Par",0.5,IF(LEFT(D26,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F27" s="12" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr"/>
-      <c r="H27" s="20">
+      <c r="F26" s="15" t="inlineStr"/>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="23">
         <f>IF(D26="","",IF(LEFT(D26,3)="Not","HIGH",IF(LEFT(D26,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>8F · Food Safety / Bezpečnosť potravín</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Trace</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>Traceability 'one step back/forward' + recall procedure
 Vysledovateľnosť „o krok späť/vpred“ + postup stiahnutia produktu</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr"/>
-      <c r="E28" s="19">
+      <c r="D27" s="21" t="inlineStr"/>
+      <c r="E27" s="22">
         <f>IF(D27="","",IF(LEFT(D27,3)="Con",1,IF(LEFT(D27,3)="Par",0.5,IF(LEFT(D27,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr"/>
-      <c r="H28" s="20">
+      <c r="F27" s="15" t="inlineStr"/>
+      <c r="G27" s="15" t="inlineStr"/>
+      <c r="H27" s="23">
         <f>IF(D27="","",IF(LEFT(D27,3)="Not","HIGH",IF(LEFT(D27,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>8F · Food Safety / Bezpečnosť potravín</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>852</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>Hygiene &amp; temperature monitoring records kept (Reg. 852/2004)
 Záznamy hygieny a monitorovania teploty vedené (nar. 852/2004)</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr"/>
-      <c r="E29" s="19">
+      <c r="D28" s="21" t="inlineStr"/>
+      <c r="E28" s="22">
         <f>IF(D28="","",IF(LEFT(D28,3)="Con",1,IF(LEFT(D28,3)="Par",0.5,IF(LEFT(D28,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F29" s="12" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="20">
+      <c r="F28" s="15" t="inlineStr"/>
+      <c r="G28" s="15" t="inlineStr"/>
+      <c r="H28" s="23">
         <f>IF(D28="","",IF(LEFT(D28,3)="Not","HIGH",IF(LEFT(D28,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>9 · Performance / Hodnotenie</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>Monitoring, measurement and analysis are performed and recorded
 Monitorovanie, meranie a analýza sa vykonávajú a zaznamenávajú</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr"/>
-      <c r="E30" s="19">
+      <c r="D29" s="21" t="inlineStr"/>
+      <c r="E29" s="22">
         <f>IF(D29="","",IF(LEFT(D29,3)="Con",1,IF(LEFT(D29,3)="Par",0.5,IF(LEFT(D29,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="12" t="inlineStr"/>
-      <c r="H30" s="20">
+      <c r="F29" s="15" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="23">
         <f>IF(D29="","",IF(LEFT(D29,3)="Not","HIGH",IF(LEFT(D29,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>9 · Performance / Hodnotenie</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>An internal audit programme is planned and carried out
 Program interných auditov je naplánovaný a vykonávaný</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr"/>
-      <c r="E31" s="19">
+      <c r="D30" s="21" t="inlineStr"/>
+      <c r="E30" s="22">
         <f>IF(D30="","",IF(LEFT(D30,3)="Con",1,IF(LEFT(D30,3)="Par",0.5,IF(LEFT(D30,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr"/>
-      <c r="H31" s="20">
+      <c r="F30" s="15" t="inlineStr"/>
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="23">
         <f>IF(D30="","",IF(LEFT(D30,3)="Not","HIGH",IF(LEFT(D30,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>9 · Performance / Hodnotenie</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>Management review meetings are held and minuted
 Preskúmania manažmentom sa konajú a vedú sa z nich zápisy</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr"/>
-      <c r="E32" s="19">
+      <c r="D31" s="21" t="inlineStr"/>
+      <c r="E31" s="22">
         <f>IF(D31="","",IF(LEFT(D31,3)="Con",1,IF(LEFT(D31,3)="Par",0.5,IF(LEFT(D31,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F32" s="12" t="inlineStr"/>
-      <c r="G32" s="12" t="inlineStr"/>
-      <c r="H32" s="20">
+      <c r="F31" s="15" t="inlineStr"/>
+      <c r="G31" s="15" t="inlineStr"/>
+      <c r="H31" s="23">
         <f>IF(D31="","",IF(LEFT(D31,3)="Not","HIGH",IF(LEFT(D31,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>10 · Improvement / Zlepšovanie</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Nonconformities are recorded and corrected
 Nezhody sú zaznamenané a odstránené</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr"/>
-      <c r="E33" s="19">
+      <c r="D32" s="21" t="inlineStr"/>
+      <c r="E32" s="22">
         <f>IF(D32="","",IF(LEFT(D32,3)="Con",1,IF(LEFT(D32,3)="Par",0.5,IF(LEFT(D32,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr"/>
-      <c r="H33" s="20">
+      <c r="F32" s="15" t="inlineStr"/>
+      <c r="G32" s="15" t="inlineStr"/>
+      <c r="H32" s="23">
         <f>IF(D32="","",IF(LEFT(D32,3)="Not","HIGH",IF(LEFT(D32,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>10 · Improvement / Zlepšovanie</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>Corrective action with root-cause analysis (CAPA log) is used
 Nápravné opatrenia s analýzou príčin (CAPA) sa používajú</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr"/>
-      <c r="E34" s="19">
+      <c r="D33" s="21" t="inlineStr"/>
+      <c r="E33" s="22">
         <f>IF(D33="","",IF(LEFT(D33,3)="Con",1,IF(LEFT(D33,3)="Par",0.5,IF(LEFT(D33,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F34" s="12" t="inlineStr"/>
-      <c r="G34" s="12" t="inlineStr"/>
-      <c r="H34" s="20">
+      <c r="F33" s="15" t="inlineStr"/>
+      <c r="G33" s="15" t="inlineStr"/>
+      <c r="H33" s="23">
         <f>IF(D33="","",IF(LEFT(D33,3)="Not","HIGH",IF(LEFT(D33,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>10 · Improvement / Zlepšovanie</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>Continual improvement is evidenced over time
 Trvalé zlepšovanie je preukázané v čase</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr"/>
-      <c r="E35" s="19">
+      <c r="D34" s="21" t="inlineStr"/>
+      <c r="E34" s="22">
         <f>IF(D34="","",IF(LEFT(D34,3)="Con",1,IF(LEFT(D34,3)="Par",0.5,IF(LEFT(D34,3)="Not",0,""))))</f>
         <v/>
       </c>
-      <c r="F35" s="12" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr"/>
-      <c r="H35" s="20">
+      <c r="F34" s="15" t="inlineStr"/>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="23">
         <f>IF(D34="","",IF(LEFT(D34,3)="Not","HIGH",IF(LEFT(D34,3)="Par","MEDIUM","")))</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>OVERALL CONFORMANCE / CELKOVÁ ZHODA →</t>
         </is>
       </c>
-      <c r="E36" s="22">
+      <c r="E35" s="25">
         <f>IF(COUNT(E9:E34)=0,"",AVERAGE(E9:E34))</f>
         <v/>
       </c>
-      <c r="F36" s="23">
+      <c r="F35" s="26">
         <f>CONCATENATE("HIGH-priority gaps / kritické medzery: ",COUNTIF(H9:H34,"HIGH"))</f>
         <v/>
       </c>
@@ -2059,14 +2164,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2076,432 +2181,424 @@
     <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMO — PREVIEW ONLY · enter your email to download the free editable file · ukážka — zadajte e-mail a stiahnite si bezplatný upraviteľný súbor</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Mock-Audit · Readiness Self-Assessment  |  Skúšobný audit · Sebahodnotenie pripravenosti</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Mock-Audit · Readiness Self-Assessment  |  Skúšobný audit · Sebahodnotenie pripravenosti</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Answer honestly as if the auditor is in the room — score auto-rolls up to Sheet 03  ·  Odpovedajte úprimne, akoby bol audítor v miestnosti — skóre sa prenáša na hárok 03</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Answer honestly as if the auditor is in the room — score auto-rolls up to Sheet 03  ·  Odpovedajte úprimne, akoby bol audítor v miestnosti — skóre sa prenáša na hárok 03</t>
-        </is>
-      </c>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Assessed by / Posúdil:</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Assessed by / Posúdil:</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr"/>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Date (DD/MM/YYYY) / Dátum:</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Date (DD/MM/YYYY) / Dátum:</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>ℹ  Yes = you could evidence it now (100%) · Partly = some evidence/gaps (50%) · No = not in place (0%). Be honest — the point is to find gaps before the auditor does.
     Áno = viete to doložiť teraz (100 %) · Čiastočne = časť dôkazov (50 %) · Nie = chýba (0 %). Buďte úprimní — cieľom je nájsť medzery skôr ako audítor.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Question / Otázka</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Answer
 Odpoveď</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Score
 Skóre</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Note / Poznámka</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="16" t="n">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Could you show a current policy, signed and dated by management?
 Viete predložiť aktuálnu politiku podpísanú a datovanú manažmentom?</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="19">
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="22">
         <f>IF(C8="","",IF(LEFT(C8,3)="Yes",1,IF(LEFT(C8,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E9" s="24" t="inlineStr"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="25" t="n">
+      <c r="E8" s="27" t="inlineStr"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Could you produce an up-to-date scope / process map of the business?
 Viete predložiť aktuálny rozsah / mapu procesov prevádzky?</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="19">
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="22">
         <f>IF(C9="","",IF(LEFT(C9,3)="Yes",1,IF(LEFT(C9,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E10" s="24" t="inlineStr"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="16" t="n">
+      <c r="E9" s="27" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Could you show this year's measurable objectives and progress?
 Viete ukázať tohtoročné merateľné ciele a pokrok?</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="19">
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="22">
         <f>IF(C10="","",IF(LEFT(C10,3)="Yes",1,IF(LEFT(C10,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E11" s="24" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="25" t="n">
+      <c r="E10" s="27" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Has your risk register been reviewed in the last 12 months?
 Bol register rizík preskúmaný za posledných 12 mesiacov?</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr"/>
-      <c r="D12" s="19">
+      <c r="C11" s="21" t="inlineStr"/>
+      <c r="D11" s="22">
         <f>IF(C11="","",IF(LEFT(C11,3)="Yes",1,IF(LEFT(C11,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E12" s="24" t="inlineStr"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="16" t="n">
+      <c r="E11" s="27" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Could you show training records for every member of staff?
 Viete predložiť záznamy o školení pre každého zamestnanca?</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr"/>
-      <c r="D13" s="19">
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="22">
         <f>IF(C12="","",IF(LEFT(C12,3)="Yes",1,IF(LEFT(C12,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E13" s="24" t="inlineStr"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="25" t="n">
+      <c r="E12" s="27" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Would staff, asked at random, know the policy and their duties?
 Poznali by náhodne oslovení zamestnanci politiku a svoje povinnosti?</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr"/>
-      <c r="D14" s="19">
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="22">
         <f>IF(C13="","",IF(LEFT(C13,3)="Yes",1,IF(LEFT(C13,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E14" s="24" t="inlineStr"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="16" t="n">
+      <c r="E13" s="27" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Is your documented information version-controlled (no undated drafts)?
 Má vaša dokumentácia riadené verzie (žiadne nedatované koncepty)?</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr"/>
-      <c r="D15" s="19">
+      <c r="C14" s="21" t="inlineStr"/>
+      <c r="D14" s="22">
         <f>IF(C14="","",IF(LEFT(C14,3)="Yes",1,IF(LEFT(C14,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E15" s="24" t="inlineStr"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="25" t="n">
+      <c r="E14" s="27" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Could you produce an approved-supplier list with evidence of approval?
 Viete predložiť zoznam schválených dodávateľov s dôkazom schválenia?</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr"/>
-      <c r="D16" s="19">
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="22">
         <f>IF(C15="","",IF(LEFT(C15,3)="Yes",1,IF(LEFT(C15,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E16" s="24" t="inlineStr"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="E15" s="27" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>(Food) Could you show a HACCP plan with CCPs and critical limits?
 (Potraviny) Viete ukázať HACCP plán s CCP a kritickými limitmi?</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr"/>
-      <c r="D17" s="19">
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="22">
         <f>IF(C16="","",IF(LEFT(C16,3)="Yes",1,IF(LEFT(C16,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E17" s="24" t="inlineStr"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="25" t="n">
+      <c r="E16" s="27" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>(Food) Could you give allergen information for every item/product?
 (Potraviny) Viete poskytnúť informácie o alergénoch pre každú položku?</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr"/>
-      <c r="D18" s="19">
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="22">
         <f>IF(C17="","",IF(LEFT(C17,3)="Yes",1,IF(LEFT(C17,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E18" s="24" t="inlineStr"/>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="E17" s="27" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Could you trace a batch one step back and one step forward in minutes?
 Viete vystopovať šaržu o krok späť a o krok vpred v priebehu minút?</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr"/>
-      <c r="D19" s="19">
+      <c r="C18" s="21" t="inlineStr"/>
+      <c r="D18" s="22">
         <f>IF(C18="","",IF(LEFT(C18,3)="Yes",1,IF(LEFT(C18,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E19" s="24" t="inlineStr"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="25" t="n">
+      <c r="E18" s="27" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Could you show monitoring records (temperatures/checks) for last month?
 Viete ukázať záznamy monitorovania (teploty/kontroly) za minulý mesiac?</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr"/>
-      <c r="D20" s="19">
+      <c r="C19" s="21" t="inlineStr"/>
+      <c r="D19" s="22">
         <f>IF(C19="","",IF(LEFT(C19,3)="Yes",1,IF(LEFT(C19,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E20" s="24" t="inlineStr"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="E19" s="27" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Have you completed at least one internal audit in the last 12 months?
 Vykonali ste aspoň jeden interný audit za posledných 12 mesiacov?</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr"/>
-      <c r="D21" s="19">
+      <c r="C20" s="21" t="inlineStr"/>
+      <c r="D20" s="22">
         <f>IF(C20="","",IF(LEFT(C20,3)="Yes",1,IF(LEFT(C20,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E21" s="24" t="inlineStr"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="25" t="n">
+      <c r="E20" s="27" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Could you produce minutes of a management review meeting?
 Viete predložiť zápis z preskúmania manažmentom?</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr"/>
-      <c r="D22" s="19">
+      <c r="C21" s="21" t="inlineStr"/>
+      <c r="D21" s="22">
         <f>IF(C21="","",IF(LEFT(C21,3)="Yes",1,IF(LEFT(C21,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E22" s="24" t="inlineStr"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="E21" s="27" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Do you keep a nonconformity / corrective-action log that is actually used?
 Vediete register nezhôd / nápravných opatrení, ktorý sa naozaj používa?</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr"/>
-      <c r="D23" s="19">
+      <c r="C22" s="21" t="inlineStr"/>
+      <c r="D22" s="22">
         <f>IF(C22="","",IF(LEFT(C22,3)="Yes",1,IF(LEFT(C22,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E23" s="24" t="inlineStr"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="25" t="n">
+      <c r="E22" s="27" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Could you show a closed-out corrective action with root-cause analysis?
 Viete ukázať uzavreté nápravné opatrenie s analýzou koreňovej príčiny?</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr"/>
-      <c r="D24" s="19">
+      <c r="C23" s="21" t="inlineStr"/>
+      <c r="D23" s="22">
         <f>IF(C23="","",IF(LEFT(C23,3)="Yes",1,IF(LEFT(C23,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E24" s="24" t="inlineStr"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="E23" s="27" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Could you show calibration / verification records for monitoring equipment?
 Viete ukázať záznamy o kalibrácii / overení meradiel?</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr"/>
-      <c r="D25" s="19">
+      <c r="C24" s="21" t="inlineStr"/>
+      <c r="D24" s="22">
         <f>IF(C24="","",IF(LEFT(C24,3)="Yes",1,IF(LEFT(C24,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E25" s="24" t="inlineStr"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="25" t="n">
+      <c r="E24" s="27" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="28" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Can you evidence continual improvement (a clear before/after)?
 Viete preukázať trvalé zlepšovanie (jasný stav pred/po)?</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr"/>
-      <c r="D26" s="19">
+      <c r="C25" s="21" t="inlineStr"/>
+      <c r="D25" s="22">
         <f>IF(C25="","",IF(LEFT(C25,3)="Yes",1,IF(LEFT(C25,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E26" s="24" t="inlineStr"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="E25" s="27" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Are records retained for the required period (≥ 12 months) and retrievable?
 Sú záznamy uchované požadovaný čas (≥ 12 mesiacov) a dohľadateľné?</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr"/>
-      <c r="D27" s="19">
+      <c r="C26" s="21" t="inlineStr"/>
+      <c r="D26" s="22">
         <f>IF(C26="","",IF(LEFT(C26,3)="Yes",1,IF(LEFT(C26,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E27" s="24" t="inlineStr"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="25" t="n">
+      <c r="E26" s="27" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>If an auditor arrived unannounced today, would your records be in order?
 Keby dnes prišiel audítor bez ohlásenia, boli by vaše záznamy v poriadku?</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr"/>
-      <c r="D28" s="19">
+      <c r="C27" s="21" t="inlineStr"/>
+      <c r="D27" s="22">
         <f>IF(C27="","",IF(LEFT(C27,3)="Yes",1,IF(LEFT(C27,3)="Par",0.5,0)))</f>
         <v/>
       </c>
-      <c r="E28" s="24" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>MOCK-AUDIT READINESS / PRIPRAVENOSŤ →</t>
         </is>
       </c>
-      <c r="D29" s="22">
+      <c r="D28" s="25">
         <f>IF(COUNT(D8:D27)=0,"",AVERAGE(D8:D27))</f>
         <v/>
       </c>
-      <c r="E29" s="26" t="inlineStr"/>
+      <c r="E28" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CA8B"/>
@@ -2534,14 +2631,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2552,294 +2649,282 @@
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMO — PREVIEW ONLY · enter your email to download the free editable file · ukážka — zadajte e-mail a stiahnite si bezplatný upraviteľný súbor</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Readiness Score &amp; Verdict  |  Skóre pripravenosti a verdikt</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Readiness Score &amp; Verdict  |  Skóre pripravenosti a verdikt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Auto-calculated from Sheets 01 &amp; 02 — the answer to 'will I pass?'  ·  Automaticky z hárkov 01 a 02 — odpoveď na otázku „prejdem?“</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Gap-analysis conformance / Zhoda z analýzy nedostatkov</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="33">
+        <f>IF('01 · Gap Analysis · Analýza'!E35="","",'01 · Gap Analysis · Analýza'!E35)</f>
+        <v/>
+      </c>
+      <c r="E4" s="31" t="n"/>
+      <c r="F4" s="32" t="n"/>
+    </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>Gap-analysis conformance / Zhoda z analýzy nedostatkov</t>
-        </is>
-      </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="30">
-        <f>IF('01 · Gap Analysis · Analýza'!E35="","",'01 · Gap Analysis · Analýza'!E35)</f>
-        <v/>
-      </c>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="29" t="n"/>
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Mock-audit readiness / Pripravenosť zo skúšobného auditu</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="33">
+        <f>IF('02 · Mock Audit · Skúška'!D28="","",'02 · Mock Audit · Skúška'!D28)</f>
+        <v/>
+      </c>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="32" t="n"/>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>Mock-audit readiness / Pripravenosť zo skúšobného auditu</t>
-        </is>
-      </c>
-      <c r="B6" s="28" t="n"/>
-      <c r="C6" s="29" t="n"/>
-      <c r="D6" s="30">
-        <f>IF('02 · Mock Audit · Skúšobný audit'!D28="","",'02 · Mock Audit · Skúšobný audit'!D28)</f>
-        <v/>
-      </c>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="29" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>OVERALL READINESS / CELKOVÁ PRIPRAVENOSŤ</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="31">
-        <f>IF(AND('01 · Gap Analysis · Analýza'!E35="",'02 · Mock Audit · Skúšobný audit'!D28=""),"",IF('01 · Gap Analysis · Analýza'!E35="",'02 · Mock Audit · Skúšobný audit'!D28,IF('02 · Mock Audit · Skúšobný audit'!D28="",'01 · Gap Analysis · Analýza'!E35,('01 · Gap Analysis · Analýza'!E35+'02 · Mock Audit · Skúšobný audit'!D28)/2)))</f>
-        <v/>
-      </c>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="29" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1"/>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="34">
+        <f>IF(AND('01 · Gap Analysis · Analýza'!E35="",'02 · Mock Audit · Skúška'!D28=""),"",IF('01 · Gap Analysis · Analýza'!E35="",'02 · Mock Audit · Skúška'!D28,IF('02 · Mock Audit · Skúška'!D28="",'01 · Gap Analysis · Analýza'!E35,('01 · Gap Analysis · Analýza'!E35+'02 · Mock Audit · Skúška'!D28)/2)))</f>
+        <v/>
+      </c>
+      <c r="E6" s="31" t="n"/>
+      <c r="F6" s="32" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>VERDICT — WILL I PASS? / VERDIKT — PREJDEM?</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>VERDICT — WILL I PASS? / VERDIKT — PREJDEM?</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="32">
+      <c r="A9" s="35">
         <f>IF(D6="","Complete Sheets 01 &amp; 02 to see your verdict / Vyplňte hárky 01 a 02",IF(D6&gt;=0.85,"🟢 LIKELY TO PASS — tidy the ambers, then book. / PRAVDEPODOBNE PREJDETE — doriešte oranžové a objednajte audit.",IF(D6&gt;=0.6,"🟠 AT RISK — close the red (HIGH) gaps before booking. / RIZIKO — pred objednaním uzavrite červené (kritické) medzery.","🔴 NOT READY — significant gaps; work through Sheet 04 first. / NEPRIPRAVENÍ — vážne medzery; najprv prejdite hárok 04.")))</f>
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="20" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>RAG BANDS / PÁSMA RAG</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>RAG BANDS / PÁSMA RAG</t>
-        </is>
-      </c>
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>🟢 ≥ 85%</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>Likely to pass — minor tidy-ups</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="39" t="inlineStr">
+        <is>
+          <t>Pravdepodobne prejdete — drobné úpravy</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>🟢 ≥ 85%</t>
-        </is>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>Likely to pass — minor tidy-ups</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>Pravdepodobne prejdete — drobné úpravy</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="n"/>
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>🟠 60–84%</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>At risk — close HIGH gaps first</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="39" t="inlineStr">
+        <is>
+          <t>Riziko — najprv kritické medzery</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>🟠 60–84%</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>At risk — close HIGH gaps first</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="36" t="inlineStr">
-        <is>
-          <t>Riziko — najprv kritické medzery</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>🔴 &lt; 60%</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>Not ready — significant work needed</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="39" t="inlineStr">
         <is>
           <t>Nepripravení — vážna práca</t>
         </is>
       </c>
-      <c r="F16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1"/>
+      <c r="F15" s="29" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>OPEN GAPS / OTVORENÉ MEDZERY</t>
+        </is>
+      </c>
+    </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>OPEN GAPS / OTVORENÉ MEDZERY</t>
-        </is>
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>HIGH priority (Not in place) / kritické (chýba)</t>
+        </is>
+      </c>
+      <c r="E18" s="43">
+        <f>COUNTIF('01 · Gap Analysis · Analýza'!H9:H34,"HIGH")</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>HIGH priority (Not in place) / kritické (chýba)</t>
-        </is>
-      </c>
-      <c r="E19" s="40">
-        <f>COUNTIF('01 · Gap Analysis · Analýza'!H9:H34,"HIGH")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>MEDIUM priority (Partial) / stredné (čiastočne)</t>
         </is>
       </c>
-      <c r="E20" s="42">
+      <c r="E19" s="45">
         <f>COUNTIF('01 · Gap Analysis · Analýza'!H9:H34,"MEDIUM")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>SECTION BREAKDOWN / ROZPIS PO SEKCIÁCH</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>SECTION BREAKDOWN / ROZPIS PO SEKCIÁCH</t>
-        </is>
-      </c>
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Section / Sekcia</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="32" t="n"/>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Conf. % / Zhoda %</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Section / Sekcia</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="n"/>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Conf. % / Zhoda %</t>
-        </is>
-      </c>
-      <c r="F23" s="29" t="n"/>
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>4 · Context / Kontext</t>
+        </is>
+      </c>
+      <c r="E23" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"4 · Context / Kontext"),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>4 · Context / Kontext</t>
-        </is>
-      </c>
-      <c r="E24" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"4 · Context / Kontext"),"—")</f>
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>5 · Leadership / Vedenie</t>
+        </is>
+      </c>
+      <c r="E24" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"5 · Leadership / Vedenie"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="35" t="inlineStr">
-        <is>
-          <t>5 · Leadership / Vedenie</t>
-        </is>
-      </c>
-      <c r="E25" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"5 · Leadership / Vedenie"),"—")</f>
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>6 · Planning / Plánovanie</t>
+        </is>
+      </c>
+      <c r="E25" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"6 · Planning / Plánovanie"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>6 · Planning / Plánovanie</t>
-        </is>
-      </c>
-      <c r="E26" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"6 · Planning / Plánovanie"),"—")</f>
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>7 · Support / Podpora</t>
+        </is>
+      </c>
+      <c r="E26" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"7 · Support / Podpora"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="35" t="inlineStr">
-        <is>
-          <t>7 · Support / Podpora</t>
-        </is>
-      </c>
-      <c r="E27" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"7 · Support / Podpora"),"—")</f>
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>8 · Operation / Prevádzka</t>
+        </is>
+      </c>
+      <c r="E27" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"8 · Operation / Prevádzka"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="35" t="inlineStr">
-        <is>
-          <t>8 · Operation / Prevádzka</t>
-        </is>
-      </c>
-      <c r="E28" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"8 · Operation / Prevádzka"),"—")</f>
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>8F · Food Safety / Bezpečnosť potravín</t>
+        </is>
+      </c>
+      <c r="E28" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"8F · Food Safety / Bezpečnosť potravín"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>8F · Food Safety / Bezpečnosť potravín</t>
-        </is>
-      </c>
-      <c r="E29" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"8F · Food Safety / Bezpečnosť potravín"),"—")</f>
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>9 · Performance / Hodnotenie</t>
+        </is>
+      </c>
+      <c r="E29" s="46">
+        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"9 · Performance / Hodnotenie"),"—")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t>9 · Performance / Hodnotenie</t>
-        </is>
-      </c>
-      <c r="E30" s="43">
-        <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"9 · Performance / Hodnotenie"),"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>10 · Improvement / Zlepšovanie</t>
         </is>
       </c>
-      <c r="E31" s="43">
+      <c r="E30" s="46">
         <f>IFERROR(AVERAGEIFS('01 · Gap Analysis · Analýza'!E9:E34,'01 · Gap Analysis · Analýza'!A9:A34,"10 · Improvement / Zlepšovanie"),"—")</f>
         <v/>
       </c>
@@ -2989,14 +3074,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3005,193 +3090,183 @@
     <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DEMO — PREVIEW ONLY · enter your email to download the free editable file · ukážka — zadajte e-mail a stiahnite si bezplatný upraviteľný súbor</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Next Steps — Close Your Gaps  |  Ďalšie kroky — vyriešte svoje medzery</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Next Steps — Close Your Gaps  |  Ďalšie kroky — vyriešte svoje medzery</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Pick the readiness kit that matches your sector &amp; standard  ·  Vyberte balík pripravenosti podľa vášho odvetvia a normy</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Pick the readiness kit that matches your sector &amp; standard  ·  Vyberte balík pripravenosti podľa vášho odvetvia a normy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>ℹ  This free tool finds the gaps. The matching paid kit gives you the ready-made templates, logs and procedures to close them — built once, audit-ready. Prices indicative; see the listing.
     Tento bezplatný nástroj nájde medzery. Príslušný platený balík vám dá hotové šablóny, záznamy a postupy na ich vyriešenie — pripravené na audit. Ceny orientačné; pozri ponuku.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1"/>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Your sector / standard
 Vaše odvetvie / norma</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Recommended kit
 Odporúčaný balík</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>From €
 Od €</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>What it closes
 Čo vyrieši</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Café · restaurant · bar · B&amp;B · hotel
 HACCP · 852/2004 · 1169/2011</t>
         </is>
       </c>
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>P14 — HACCP Readiness Pack
 (Cafés &amp; Restaurants)</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>HACCP plan, CCP/PRP logs, allergen matrix, traceability, training, CAPA</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="48" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Food manufacturing (GFSI)
 ISO 22000 · FSSC 22000 v7</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>P15 — ISO 22000 / FSSC 22000
 Food Safety Management Kit</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D8" s="50" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>Full FSMS spine: doc-control, internal audit, mgmt review, CAPA, calibration</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Food manufacturing
 BRCGS · IFS Food</t>
         </is>
       </c>
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>P16 — BRCGS / IFS Document-Control
 &amp; Audit-Readiness Suite</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>Master document list, supplier approval, internal audit — the #1 NC area</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="48" t="inlineStr">
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Non-food manufacturing
 ISO 9001</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>P17 — ISO 9001 Quality-Management
 Audit-Readiness Pack</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="50" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>ISO 9001 clause 4–10 spine for B2B customer-required certification</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="44" t="inlineStr">
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Already certified FSSC v6
 upgrade to v7 by Apr 2028</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B10" s="48" t="inlineStr">
         <is>
           <t>P18 — FSSC 22000 V7
 Transition Pack</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="47" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>v6→v7 delta gap-analysis, internal audit &amp; management-review updates</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1"/>
-    <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>Auditors &amp; consultants / Audítori a konzultanti → P19 Auditor Edition · P20 Multi-Client Console (from €149)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1"/>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Positioning: audit-ready packs that satisfy a TÜV-style certifier auditing you to ISO / HACCP / BRCGS / IFS — not 'TÜV templates'. · Balíky pripravené na audit certifikačným orgánom (štýl TÜV) podľa ISO / HACCP / BRCGS / IFS.</t>
         </is>
